--- a/data/universidades_colegios.xlsx
+++ b/data/universidades_colegios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrei.flores\Documents\Trabajo\Walk Out\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udlaec-my.sharepoint.com/personal/martin_bueno_udla_edu_ec/Documents/UDLA/PASANTIAS INV. MERCADOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2380E573-F7D9-4776-9A81-27579AE0AA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="8_{B619FD1A-F798-4265-868D-CE76D3D28100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74259468-4F28-4855-872C-2143427E71CF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8D134F6-B4B6-4ADE-B048-B6F71037BA3C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C8D134F6-B4B6-4ADE-B048-B6F71037BA3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Universidades" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="1005">
   <si>
     <t>UNIVERSIDAD</t>
   </si>
@@ -2281,6 +2281,777 @@
   </si>
   <si>
     <t>PUBLICA</t>
+  </si>
+  <si>
+    <t>SEDES</t>
+  </si>
+  <si>
+    <t>CONSERVATORIO SUPERIOR DE MUSICA JAIME MOLA</t>
+  </si>
+  <si>
+    <t>CONSERVATORIO SUPERIOR NACIONAL DE MUSICA</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR  TECNOLOGICO CONSEJO PROVINCIAL DE PICHINCHA</t>
+  </si>
+  <si>
+    <t>Campus Riofrío</t>
+  </si>
+  <si>
+    <t>Matriz</t>
+  </si>
+  <si>
+    <t>Campus Comunitario</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR  TECNOLOGICO ISMAC</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR PEDAGOGICO MANUELA CAÑIZARES</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO  VIDA NUEVA</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO BERNARDO O'HIGGINS</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CEMLAD</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CENESTUR</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CENTRAL TECNICO</t>
+  </si>
+  <si>
+    <t>Campus de Arte, Ciencia y Labor</t>
+  </si>
+  <si>
+    <t>Campus Principal</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CINCO DE JUNIO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO COMPU SUR</t>
+  </si>
+  <si>
+    <t>Campus Matriz</t>
+  </si>
+  <si>
+    <t>Campus Norte</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CORDILLERA</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CORPORATIVO EDWARDS DEMING</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CRE-SER</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CRUZ ROJA ECUATORIANA</t>
+  </si>
+  <si>
+    <t>Campus 2</t>
+  </si>
+  <si>
+    <t>Campus 1</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO CUEST T.V.</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DAVID P AUSUBEL</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE ARTES VISUALES</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE CINE Y ACTUACION</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE DESARROLLO HUMANO CRE-SER</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE ESTUDIOS INTEGRALES ITSEI</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE FUTBOL DE QUITO - ISTFQ</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE LA VERA CRUZ</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE MARKETING Y ADMINISTRACION</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE TECNOLOGIAS APROPIADAS</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE TECNOLOGIAS INTELIGENTES (INSTTI)</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DE TURISMO Y PATRIMONIO YAVIRAC</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DEL TRANSPORTE</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO DISMOD</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO ECUATORIANO DE PRODUCTIVIDAD</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO EL PACIFICO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO INTEGRACION ANDINA</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO INTERNACIONAL ITI</t>
+  </si>
+  <si>
+    <t>Campus &amp; de Diciembre</t>
+  </si>
+  <si>
+    <t>Campus Campus Ramírez Dávalos</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO ISMAC</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO JAPON</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO KACHARIY</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO LENDAN</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO LIBERTAD</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO LOS ANDES DE ESTUDIOS SOCIALES - ILADES</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO MAYOR PEDRO TRAVERSARI</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO MEJIA</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO PARA EL DESARROLLO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO PICHINCHA</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO POLICIA NACIONAL</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO QUITO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO QUITO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO RUMIÑAHUI</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO SUCRE</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO SUDAMERICANO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO SUPERARSE</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO TECNOECUATORIANO</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO UNIVERSITEC</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGICO YARUQUI</t>
+  </si>
+  <si>
+    <t>INSTITUTO SUPERIOR TECNOLOGIO ESCULAPIO</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR ALEMAN</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR BENITO JUAREZ</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR CEMLAD</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR CINCO DE JUNIO</t>
+  </si>
+  <si>
+    <t>-0.19637326606365407</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49754740044146</t>
+  </si>
+  <si>
+    <t>-0.17060693521022421</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.47271096911912</t>
+  </si>
+  <si>
+    <t>-0.21005000050881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48934739801486</t>
+  </si>
+  <si>
+    <t>-0.19433089094016154</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4859908728689</t>
+  </si>
+  <si>
+    <t>-0.17303319949543147</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48567831091466</t>
+  </si>
+  <si>
+    <t>-0.206811330990169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50113463514828</t>
+  </si>
+  <si>
+    <t>-0.2610494238419852</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.53548633855044</t>
+  </si>
+  <si>
+    <t>-0.20610530547328876</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50629709910308</t>
+  </si>
+  <si>
+    <t>-0.21606516633456624</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.40184758716924</t>
+  </si>
+  <si>
+    <t>-0.18930855627903553</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50347576067617</t>
+  </si>
+  <si>
+    <t>-0.3383612830534746</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.55048220753847</t>
+  </si>
+  <si>
+    <t>-0.1806777808003768</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49378701023907</t>
+  </si>
+  <si>
+    <t>-0.24378623642937344</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.51731310530145</t>
+  </si>
+  <si>
+    <t>-0.20357693688606876</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49871008101836</t>
+  </si>
+  <si>
+    <t>-0.15208324740943116</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.47952888767541</t>
+  </si>
+  <si>
+    <t>-0.16788897426146226</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48167324062217</t>
+  </si>
+  <si>
+    <t>-0.25819790038579854</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52635604022926</t>
+  </si>
+  <si>
+    <t>-0.24783405361507319</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52041646237487</t>
+  </si>
+  <si>
+    <t>-0.2621567867230507</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52657386160216</t>
+  </si>
+  <si>
+    <t>-0.173337490271496</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48017850299321</t>
+  </si>
+  <si>
+    <t>-0.15524504219923843</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48840039798723</t>
+  </si>
+  <si>
+    <t>-0.15357493679460293</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48994032933741</t>
+  </si>
+  <si>
+    <t>-0.19280697963436585</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49624495825024</t>
+  </si>
+  <si>
+    <t>-0.17967427821313997</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49433499821102</t>
+  </si>
+  <si>
+    <t>-0.14894232628581708</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.47664858018953</t>
+  </si>
+  <si>
+    <t>-0.24778149555389664</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52944835826936</t>
+  </si>
+  <si>
+    <t>-0.11667257804132186</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49432653076427</t>
+  </si>
+  <si>
+    <t>-0.17866133706385534</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49485515825056</t>
+  </si>
+  <si>
+    <t>-0.20854779499980522</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48285437153724</t>
+  </si>
+  <si>
+    <t>-0.19250035493363762</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49622866103529</t>
+  </si>
+  <si>
+    <t>-0.18298503710188654</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48796450043703</t>
+  </si>
+  <si>
+    <t>-0.16632643690465973</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.45193144261701</t>
+  </si>
+  <si>
+    <t>-0.19605046605383677</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50427887153363</t>
+  </si>
+  <si>
+    <t>-0.17559313702914428</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.47605215825119</t>
+  </si>
+  <si>
+    <t>-0.2110869950488264</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49379565826575</t>
+  </si>
+  <si>
+    <t>-0.21230537457956183</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48531334086935</t>
+  </si>
+  <si>
+    <t>-0.22485909520972197</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.51668297153648</t>
+  </si>
+  <si>
+    <t>-0.12146906349439221</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49992157149087</t>
+  </si>
+  <si>
+    <t>-0.17246819459516796</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48754134262404</t>
+  </si>
+  <si>
+    <t>-0.19749203728028705</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49601010043827</t>
+  </si>
+  <si>
+    <t>-0.19242957962942553</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4963067582455</t>
+  </si>
+  <si>
+    <t>-0.243887739314632</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.53434098717834</t>
+  </si>
+  <si>
+    <t>-0.20079710139707166</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48599843694234</t>
+  </si>
+  <si>
+    <t>-0.2006033961976539</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49828117580732</t>
+  </si>
+  <si>
+    <t>-0.21605443754444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.40183685826008</t>
+  </si>
+  <si>
+    <t>-0.04747244823118024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.44787951002876</t>
+  </si>
+  <si>
+    <t>-0.20465133737424376</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48838630044142</t>
+  </si>
+  <si>
+    <t>-0.17540569464672406</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50191445825861</t>
+  </si>
+  <si>
+    <t>-0.18485572355426583</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49068088716943</t>
+  </si>
+  <si>
+    <t>-0.21089919504093485</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49389942935245</t>
+  </si>
+  <si>
+    <t>-0.28212119497640886</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.5555158715349</t>
+  </si>
+  <si>
+    <t>-0.5102739018436069</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.57587570049971</t>
+  </si>
+  <si>
+    <t>-0.22724552259120942</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49953230043448</t>
+  </si>
+  <si>
+    <t>-0.18451558144959163</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49354589180484</t>
+  </si>
+  <si>
+    <t>-0.21026662660344342</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50114073904702</t>
+  </si>
+  <si>
+    <t>-0.16311160636735625</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48813428712184</t>
+  </si>
+  <si>
+    <t>-0.19263479481865473</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49697040044288</t>
+  </si>
+  <si>
+    <t>-0.22730149662944216</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49954678715585</t>
+  </si>
+  <si>
+    <t>-0.33909492511307127</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.43994102699843</t>
+  </si>
+  <si>
+    <t>-0.18933286599193458</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48252965825606</t>
+  </si>
+  <si>
+    <t>-0.19641040847554647</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4956169293413</t>
+  </si>
+  <si>
+    <t>-0.18406315509104937</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49083496463213</t>
+  </si>
+  <si>
+    <t>-0.3058046965473165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.45040288718502</t>
+  </si>
+  <si>
+    <t>-0.2394577954374538</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52590958717006</t>
+  </si>
+  <si>
+    <t>-0.20464539496980017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49256515825978</t>
+  </si>
+  <si>
+    <t>-0.16268493687888388</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.32013650043208</t>
+  </si>
+  <si>
+    <t>-0.17831892292139687</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48882070316725</t>
+  </si>
+  <si>
+    <t>-0.2704837377228612</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.53202942360107</t>
+  </si>
+  <si>
+    <t>-0.24578557655428554</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52887299071584</t>
+  </si>
+  <si>
+    <t>-0.2440305379463556</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.51728364262743</t>
+  </si>
+  <si>
+    <t>-0.25822230230455817</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.52634245834878</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR CORPORATIVO EDWARDS  DEMING</t>
+  </si>
+  <si>
+    <t>-0.15357493678884288</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4899296004286</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR DAVID P AUSUBEL</t>
+  </si>
+  <si>
+    <t>-0.11653204998362945</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49432605822892</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR DE RADIO Y TELEVISION</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR DE TECNOLOGIAS APROPIADAS</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR DISMOD</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR ECUATORIANO DE PRODUCTIVIDAD</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR ESTETICA INTEGRAL</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR GSSOT</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR INTEGRACION ANDINA</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR JAPON</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR LENDAN</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR LIBERTAD</t>
+  </si>
+  <si>
+    <t>INSTITUTO TECNOLOGICO SUPERIOR PARA EL DESARROLLO</t>
+  </si>
+  <si>
+    <t>UNIVERSIDAD DEL PACIFICO ESCUELA DE NEGOCIOS</t>
+  </si>
+  <si>
+    <t>-0.19016910838686898</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49148130043709</t>
+  </si>
+  <si>
+    <t>-0.2111406389947835</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49381711608295</t>
+  </si>
+  <si>
+    <t>-0.17244673698827578</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.48757352934061</t>
+  </si>
+  <si>
+    <t>-0.1975134948682296</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4959993715371</t>
+  </si>
+  <si>
+    <t>-0.18299576247501295</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4879645011182</t>
+  </si>
+  <si>
+    <t>-0.3380144602104663</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4508439059091</t>
+  </si>
+  <si>
+    <t>-0.24377295738108076</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.53438771180554</t>
+  </si>
+  <si>
+    <t>-0.04821625163225017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.44791292933272</t>
+  </si>
+  <si>
+    <t>-0.17542167325940347</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.50189135736989</t>
+  </si>
+  <si>
+    <t>-0.18484499473332708</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49064870044164</t>
+  </si>
+  <si>
+    <t>-0.20638896468108506</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.49849901604622</t>
+  </si>
+  <si>
+    <t>-0.17130230965233095</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -78.4756494077095</t>
   </si>
 </sst>
 </file>
@@ -2310,7 +3081,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2346,11 +3117,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2386,13 +3168,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2405,108 +3203,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2622,6 +3318,123 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2636,29 +3449,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6865A3AE-C400-41AA-AD8E-63AFBB46D404}" name="Tabla1" displayName="Tabla1" ref="A1:F27" totalsRowShown="0" tableBorderDxfId="12">
-  <autoFilter ref="A1:F27" xr:uid="{6865A3AE-C400-41AA-AD8E-63AFBB46D404}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6865A3AE-C400-41AA-AD8E-63AFBB46D404}" name="Tabla1" displayName="Tabla1" ref="A1:F112" totalsRowShown="0" tableBorderDxfId="6">
+  <autoFilter ref="A1:F112" xr:uid="{6865A3AE-C400-41AA-AD8E-63AFBB46D404}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{ED353B84-CAC0-4ECD-884A-2B01698D69D2}" name="UNIVERSIDAD" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{3998A60B-B180-4623-A7FE-01FF28CD2067}" name="FINANCIAMIENTO" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{43BBCAA3-CA97-49AE-811F-A535059A6570}" name="CAMPUS" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{82D3631F-C599-471E-87AD-D65FED7C7889}" name="LATITUD" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{DCD7B1A0-B314-438F-8A78-5AD12E6F6560}" name="LONGITUD" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{8467B8B5-E93A-402A-9160-F014EB7F6E30}" name="CODIGO POSTAL" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{ED353B84-CAC0-4ECD-884A-2B01698D69D2}" name="UNIVERSIDAD" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{3998A60B-B180-4623-A7FE-01FF28CD2067}" name="FINANCIAMIENTO" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{43BBCAA3-CA97-49AE-811F-A535059A6570}" name="CAMPUS" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{82D3631F-C599-471E-87AD-D65FED7C7889}" name="LATITUD" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{DCD7B1A0-B314-438F-8A78-5AD12E6F6560}" name="LONGITUD" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{8467B8B5-E93A-402A-9160-F014EB7F6E30}" name="CODIGO POSTAL" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C4C865B6-50CF-4A57-8661-35DB203C7BF8}" name="Tabla2" displayName="Tabla2" ref="A1:E220" totalsRowShown="0" tableBorderDxfId="5">
-  <autoFilter ref="A1:E220" xr:uid="{C4C865B6-50CF-4A57-8661-35DB203C7BF8}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{86566C75-3618-4272-935C-195F9C7374A2}" name="COLEGIO" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{C96F32DC-378B-4C97-B2D4-F586D8D34017}" name="TIPO" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{C9A99512-CD89-4155-A1AD-3048FCB70CE9}" name="LATITUD" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{79E30D55-621A-483A-BA07-A351CD927D48}" name="LONGITUD" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{BAAC5D05-B98C-48B2-B081-8B52A64EDE2B}" name="CODIGO POSTAL" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C4C865B6-50CF-4A57-8661-35DB203C7BF8}" name="Tabla2" displayName="Tabla2" ref="A1:F220" totalsRowShown="0" tableBorderDxfId="13">
+  <autoFilter ref="A1:F220" xr:uid="{C4C865B6-50CF-4A57-8661-35DB203C7BF8}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{86566C75-3618-4272-935C-195F9C7374A2}" name="COLEGIO" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{4CA70A5A-3D77-4D4E-930A-F39B998983CB}" name="SEDES" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{C96F32DC-378B-4C97-B2D4-F586D8D34017}" name="TIPO" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{C9A99512-CD89-4155-A1AD-3048FCB70CE9}" name="LATITUD" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{79E30D55-621A-483A-BA07-A351CD927D48}" name="LONGITUD" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{BAAC5D05-B98C-48B2-B081-8B52A64EDE2B}" name="CODIGO POSTAL" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2981,18 +3795,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE27000-3672-46D0-A176-5DC961982A67}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F112"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="80.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" customWidth="1"/>
-    <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.453125" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.26953125" customWidth="1"/>
+    <col min="4" max="4" width="38.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3012,7 +3826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>744</v>
       </c>
@@ -3032,7 +3846,7 @@
         <v>170124</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>744</v>
       </c>
@@ -3052,7 +3866,7 @@
         <v>170513</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>744</v>
       </c>
@@ -3072,7 +3886,7 @@
         <v>170517</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>12</v>
       </c>
@@ -3092,7 +3906,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
@@ -3112,7 +3926,7 @@
         <v>170201</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
@@ -3132,7 +3946,7 @@
         <v>170135</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -3152,7 +3966,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
@@ -3172,7 +3986,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
@@ -3192,7 +4006,7 @@
         <v>170129</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>745</v>
       </c>
@@ -3212,7 +4026,7 @@
         <v>170301</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>742</v>
       </c>
@@ -3232,7 +4046,7 @@
         <v>171103</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>35</v>
       </c>
@@ -3252,7 +4066,7 @@
         <v>170147</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
@@ -3272,7 +4086,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>41</v>
       </c>
@@ -3292,7 +4106,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
@@ -3312,7 +4126,7 @@
         <v>170411</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>47</v>
       </c>
@@ -3332,7 +4146,7 @@
         <v>170517</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>47</v>
       </c>
@@ -3352,7 +4166,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>54</v>
       </c>
@@ -3372,7 +4186,7 @@
         <v>170134</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>57</v>
       </c>
@@ -3392,7 +4206,7 @@
         <v>170143</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
@@ -3412,7 +4226,7 @@
         <v>170138</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>57</v>
       </c>
@@ -3432,7 +4246,7 @@
         <v>170146</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
@@ -3452,7 +4266,7 @@
         <v>170901</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
@@ -3472,7 +4286,7 @@
         <v>170103</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>73</v>
       </c>
@@ -3492,7 +4306,7 @@
         <v>170516</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>76</v>
       </c>
@@ -3512,7 +4326,7 @@
         <v>170147</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>76</v>
       </c>
@@ -3530,6 +4344,1704 @@
       </c>
       <c r="F27" s="14">
         <v>170129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>822</v>
+      </c>
+      <c r="F28" s="21">
+        <v>170102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>750</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>824</v>
+      </c>
+      <c r="F29" s="14">
+        <v>170513</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="F30" s="14">
+        <v>170143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>828</v>
+      </c>
+      <c r="F31" s="14">
+        <v>170201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>830</v>
+      </c>
+      <c r="F32" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>832</v>
+      </c>
+      <c r="F33" s="14">
+        <v>170402</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>834</v>
+      </c>
+      <c r="F34" s="14">
+        <v>170148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>836</v>
+      </c>
+      <c r="F35" s="14">
+        <v>170402</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>838</v>
+      </c>
+      <c r="F36" s="14">
+        <v>170184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>756</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>840</v>
+      </c>
+      <c r="F37" s="14">
+        <v>170129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>842</v>
+      </c>
+      <c r="F38" s="14">
+        <v>170705</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="F39" s="14">
+        <v>170509</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="F40" s="14">
+        <v>170121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>848</v>
+      </c>
+      <c r="F41" s="14">
+        <v>170520</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>763</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>850</v>
+      </c>
+      <c r="F42" s="14">
+        <v>170138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="F43" s="14">
+        <v>170513</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="F44" s="14">
+        <v>170148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>856</v>
+      </c>
+      <c r="F45" s="14">
+        <v>170601</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F46" s="14">
+        <v>170148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>767</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>860</v>
+      </c>
+      <c r="F47" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>862</v>
+      </c>
+      <c r="F48" s="14">
+        <v>170512</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="11" t="s">
+        <v>769</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>864</v>
+      </c>
+      <c r="F49" s="14">
+        <v>170517</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>866</v>
+      </c>
+      <c r="F50" s="14">
+        <v>170520</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>773</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>868</v>
+      </c>
+      <c r="F51" s="14">
+        <v>170147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>870</v>
+      </c>
+      <c r="F52" s="14">
+        <v>170138</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="F53" s="14">
+        <v>170524</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>874</v>
+      </c>
+      <c r="F54" s="14">
+        <v>170103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="F55" s="14">
+        <v>170102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>878</v>
+      </c>
+      <c r="F56" s="14">
+        <v>170143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="F57" s="14">
+        <v>170520</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>882</v>
+      </c>
+      <c r="F58" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>884</v>
+      </c>
+      <c r="F59" s="14">
+        <v>170124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>886</v>
+      </c>
+      <c r="F60" s="14">
+        <v>170111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>887</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>888</v>
+      </c>
+      <c r="F61" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>890</v>
+      </c>
+      <c r="F62" s="14">
+        <v>170403</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>784</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>892</v>
+      </c>
+      <c r="F63" s="14">
+        <v>170136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="F64" s="14">
+        <v>170401</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="F65" s="14">
+        <v>170103</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>898</v>
+      </c>
+      <c r="F66" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="F67" s="14">
+        <v>170524</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>902</v>
+      </c>
+      <c r="F68" s="14">
+        <v>170129</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>790</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="F69" s="14">
+        <v>170148</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>906</v>
+      </c>
+      <c r="F70" s="14">
+        <v>170522</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="F71" s="14">
+        <v>170520</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>794</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>910</v>
+      </c>
+      <c r="F72" s="14">
+        <v>170184</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>912</v>
+      </c>
+      <c r="F73" s="14">
+        <v>170120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="19" t="s">
+        <v>796</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>913</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="F74" s="14">
+        <v>170902</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="19" t="s">
+        <v>797</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>916</v>
+      </c>
+      <c r="F75" s="14">
+        <v>170147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="F76" s="14">
+        <v>170515</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>799</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>919</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="F77" s="14">
+        <v>170403</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="19" t="s">
+        <v>800</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>921</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="F78" s="14">
+        <v>170708</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="19" t="s">
+        <v>801</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>924</v>
+      </c>
+      <c r="F79" s="14">
+        <v>171112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>802</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>925</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>926</v>
+      </c>
+      <c r="F80" s="14">
+        <v>170403</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>803</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>927</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>928</v>
+      </c>
+      <c r="F81" s="14">
+        <v>170147</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>930</v>
+      </c>
+      <c r="F82" s="14">
+        <v>170402</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="19" t="s">
+        <v>805</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>931</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="F83" s="14">
+        <v>170104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>806</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>933</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>934</v>
+      </c>
+      <c r="F84" s="14">
+        <v>170515</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="19" t="s">
+        <v>807</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>936</v>
+      </c>
+      <c r="F85" s="14">
+        <v>170403</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>937</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="F86" s="14">
+        <v>171103</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="19" t="s">
+        <v>809</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>939</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>940</v>
+      </c>
+      <c r="F87" s="14">
+        <v>170518</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="19" t="s">
+        <v>810</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>941</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>942</v>
+      </c>
+      <c r="F88" s="14">
+        <v>170129</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="19" t="s">
+        <v>811</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>944</v>
+      </c>
+      <c r="F89" s="14">
+        <v>170508</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="19" t="s">
+        <v>812</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>946</v>
+      </c>
+      <c r="F90" s="14">
+        <v>171102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="19" t="s">
+        <v>813</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>947</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>948</v>
+      </c>
+      <c r="F91" s="14">
+        <v>170602</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>814</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="F92" s="14">
+        <v>170143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="19" t="s">
+        <v>815</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>951</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>952</v>
+      </c>
+      <c r="F93" s="14">
+        <v>170908</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>953</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>954</v>
+      </c>
+      <c r="F94" s="14">
+        <v>170102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="19" t="s">
+        <v>817</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>956</v>
+      </c>
+      <c r="F95" s="14">
+        <v>170606</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="19" t="s">
+        <v>818</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>957</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>958</v>
+      </c>
+      <c r="F96" s="14">
+        <v>170111</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="19" t="s">
+        <v>819</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>959</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>960</v>
+      </c>
+      <c r="F97" s="14">
+        <v>170121</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="19" t="s">
+        <v>820</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="F98" s="14">
+        <v>170148</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="19" t="s">
+        <v>963</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>964</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>965</v>
+      </c>
+      <c r="F99" s="20">
+        <v>170517</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="19" t="s">
+        <v>966</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>967</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>968</v>
+      </c>
+      <c r="F100" s="21">
+        <v>170103</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="19" t="s">
+        <v>969</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F101" s="14"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="19" t="s">
+        <v>970</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="F102" s="14">
+        <v>170403</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="19" t="s">
+        <v>971</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="F103" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="F104" s="14">
+        <v>170524</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>973</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="F105" s="14">
+        <v>170135</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>974</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="F106" s="14">
+        <v>171103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="19" t="s">
+        <v>975</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="F107" s="14">
+        <v>170148</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>976</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="F108" s="14">
+        <v>170120</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="19" t="s">
+        <v>977</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="F109" s="14">
+        <v>170147</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="19" t="s">
+        <v>978</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F110" s="14">
+        <v>170515</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>979</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F111" s="14">
+        <v>170143</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="18" t="s">
+        <v>980</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F112" s="1">
+        <v>170504</v>
       </c>
     </row>
   </sheetData>
@@ -3542,3756 +6054,3979 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4DC898-E646-4CCA-B678-2BC7A65E8FAC}">
-  <dimension ref="A1:G220"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H220"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="83.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>83</v>
       </c>
       <c r="B1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C1" t="s">
         <v>741</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>740</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="9">
+      <c r="F2" s="9">
         <v>170515</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="9">
+      <c r="F3" s="9">
         <v>170102</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="9">
+      <c r="F4" s="9">
         <v>170157</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="9">
+      <c r="F5" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="9">
+      <c r="F6" s="9">
         <v>170156</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="9">
+      <c r="F7" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="9">
+      <c r="F8" s="9">
         <v>170149</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="9">
+      <c r="F9" s="9">
         <v>170104</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="9">
+      <c r="F10" s="9">
         <v>170109</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="9">
+      <c r="F11" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="9">
+      <c r="F12" s="9">
         <v>170147</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E13" s="9">
+      <c r="F13" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="D14" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="9">
+      <c r="F14" s="9">
         <v>170517</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="9">
+      <c r="F15" s="9">
         <v>170801</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E16" s="9">
+      <c r="F16" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="9">
+      <c r="F17" s="9">
         <v>170143</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="D18" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="E18" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="9">
+      <c r="F18" s="9">
         <v>170104</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="E19" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="9">
+      <c r="F19" s="9">
         <v>170307</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="D20" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="E20" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="9">
+      <c r="F20" s="9">
         <v>170136</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E21" s="9">
+      <c r="F21" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="9">
+      <c r="F22" s="9">
         <v>170521</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="D23" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="9">
+      <c r="F23" s="9">
         <v>170521</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="D24" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E24" s="9">
+      <c r="F24" s="9">
         <v>170102</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E25" s="9">
+      <c r="F25" s="9">
         <v>171103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="D26" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="E26" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="9">
+      <c r="F26" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="D27" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="E27" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="9">
+      <c r="F27" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="D28" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="E28" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="E28" s="9">
+      <c r="F28" s="9">
         <v>170803</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="9"/>
+      <c r="C29" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="D29" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="E29" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E29" s="9">
+      <c r="F29" s="9">
         <v>170517</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="D30" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="E30" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="9">
+      <c r="F30" s="9">
         <v>170310</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="D31" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="E31" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="E31" s="9">
+      <c r="F31" s="9">
         <v>170120</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="E32" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="9">
+      <c r="F32" s="9">
         <v>170514</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="E33" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E33" s="9">
+      <c r="F33" s="9">
         <v>170521</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="E34" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="9">
+      <c r="F34" s="9">
         <v>170135</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D35" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="E35" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="E35" s="9">
+      <c r="F35" s="9">
         <v>170514</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="10" t="s">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="E36" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E36" s="9">
+      <c r="F36" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="E37" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E37" s="9">
+      <c r="F37" s="9">
         <v>170134</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="10" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="E38" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E38" s="9">
+      <c r="F38" s="9">
         <v>170136</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="E39" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E39" s="9">
+      <c r="F39" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="D40" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="E40" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="E40" s="9">
+      <c r="F40" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="D41" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="E41" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="E41" s="9">
+      <c r="F41" s="9">
         <v>170141</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="9"/>
+      <c r="C42" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="D42" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="E42" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="E42" s="9">
+      <c r="F42" s="9">
         <v>170524</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="10" t="s">
+      <c r="B43" s="9"/>
+      <c r="C43" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="E43" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="E43" s="9">
+      <c r="F43" s="9">
         <v>170528</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="E44" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="E44" s="9">
+      <c r="F44" s="9">
         <v>170132</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="D45" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="E45" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E45" s="9">
+      <c r="F45" s="9">
         <v>170147</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="E46" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="E46" s="9">
+      <c r="F46" s="9">
         <v>170804</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="D47" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="E47" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="E47" s="9">
+      <c r="F47" s="9">
         <v>170170</v>
       </c>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="10" t="s">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="E48" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="E48" s="9">
+      <c r="F48" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="10" t="s">
+      <c r="B49" s="9"/>
+      <c r="C49" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="E49" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E49" s="9">
+      <c r="F49" s="9">
         <v>170521</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="9"/>
+      <c r="C50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="D50" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="E50" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E50" s="9">
+      <c r="F50" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="9"/>
+      <c r="C51" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="D51" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="E51" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E51" s="9">
+      <c r="F51" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="9"/>
+      <c r="C52" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="D52" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="E52" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="E52" s="9">
+      <c r="F52" s="9">
         <v>170147</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="D53" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="E53" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="E53" s="9">
+      <c r="F53" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="E54" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="E54" s="9">
+      <c r="F54" s="9">
         <v>170207</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" s="10" t="s">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="E55" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="E55" s="9">
+      <c r="F55" s="9">
         <v>170207</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C56" s="10" t="s">
+      <c r="B56" s="9"/>
+      <c r="C56" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="E56" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="E56" s="9">
+      <c r="F56" s="9">
         <v>170129</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" s="10" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="E57" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="9">
+      <c r="F57" s="9">
         <v>170132</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="D58" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="E58" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="E58" s="9">
+      <c r="F58" s="9">
         <v>170104</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="10" t="s">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="E59" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="E59" s="9">
+      <c r="F59" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B60" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" s="10" t="s">
+      <c r="B60" s="9"/>
+      <c r="C60" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="E60" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E60" s="9">
+      <c r="F60" s="9">
         <v>170903</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" s="10" t="s">
+      <c r="B61" s="9"/>
+      <c r="C61" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="E61" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="E61" s="9">
+      <c r="F61" s="9">
         <v>170208</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="D62" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="E62" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="E62" s="9">
+      <c r="F62" s="9">
         <v>170135</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" s="10" t="s">
+      <c r="B63" s="9"/>
+      <c r="C63" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="E63" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E63" s="9">
+      <c r="F63" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" s="10" t="s">
+      <c r="B64" s="9"/>
+      <c r="C64" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D64" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="E64" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E64" s="9">
+      <c r="F64" s="9">
         <v>170804</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65" s="10" t="s">
+      <c r="B65" s="9"/>
+      <c r="C65" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="E65" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="E65" s="9">
+      <c r="F65" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" s="10" t="s">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="E66" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="E66" s="9">
+      <c r="F66" s="9">
         <v>170109</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="10" t="s">
+      <c r="B67" s="9"/>
+      <c r="C67" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="E67" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="E67" s="9">
+      <c r="F67" s="9">
         <v>170130</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C68" s="10" t="s">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="E68" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="E68" s="9">
+      <c r="F68" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="D69" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="E69" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="E69" s="9">
+      <c r="F69" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="9"/>
+      <c r="C70" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="D70" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="E70" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="E70" s="9">
+      <c r="F70" s="9">
         <v>170513</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" s="10" t="s">
+      <c r="B71" s="9"/>
+      <c r="C71" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="E71" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E71" s="9">
+      <c r="F71" s="9">
         <v>170310</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="D72" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="E72" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="E72" s="9">
+      <c r="F72" s="9">
         <v>170136</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="9"/>
+      <c r="C73" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="D73" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="E73" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="E73" s="9">
+      <c r="F73" s="9">
         <v>170134</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="D74" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="E74" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="E74" s="9">
+      <c r="F74" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="D75" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="E75" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="E75" s="9">
+      <c r="F75" s="9">
         <v>170527</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="D76" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="E76" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="E76" s="9">
+      <c r="F76" s="9">
         <v>170129</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C77" s="10" t="s">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="E77" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="E77" s="9">
+      <c r="F77" s="9">
         <v>170401</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="D78" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="E78" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="E78" s="9">
+      <c r="F78" s="9">
         <v>170120</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" s="10" t="s">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="E79" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E79" s="9">
+      <c r="F79" s="9">
         <v>170133</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="D80" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="E80" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="E80" s="9">
+      <c r="F80" s="9">
         <v>170503</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" s="10" t="s">
+      <c r="B81" s="9"/>
+      <c r="C81" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D81" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="E81" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="E81" s="9">
+      <c r="F81" s="9">
         <v>170170</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" s="10" t="s">
+      <c r="B82" s="9"/>
+      <c r="C82" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="E82" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="E82" s="9">
+      <c r="F82" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="D83" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="E83" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="E83" s="9">
+      <c r="F83" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="9"/>
+      <c r="C84" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="D84" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="E84" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="E84" s="9">
+      <c r="F84" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="9"/>
+      <c r="C85" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="D85" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="E85" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="E85" s="9">
+      <c r="F85" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C86" s="10" t="s">
+      <c r="B86" s="9"/>
+      <c r="C86" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D86" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="E86" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="9">
+      <c r="F86" s="9">
         <v>170129</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C87" s="10" t="s">
+      <c r="B87" s="9"/>
+      <c r="C87" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="E87" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="E87" s="9">
+      <c r="F87" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C88" s="10" t="s">
+      <c r="B88" s="9"/>
+      <c r="C88" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="E88" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="E88" s="9">
+      <c r="F88" s="9">
         <v>170105</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B89" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C89" s="10" t="s">
+      <c r="B89" s="9"/>
+      <c r="C89" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D89" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="E89" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="E89" s="9">
+      <c r="F89" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="9"/>
+      <c r="C90" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="D90" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="E90" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="E90" s="9">
+      <c r="F90" s="9">
         <v>170130</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="B91" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C91" s="10" t="s">
+      <c r="B91" s="9"/>
+      <c r="C91" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D91" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="E91" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="E91" s="9">
+      <c r="F91" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="9"/>
+      <c r="C92" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="D92" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="E92" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="E92" s="9">
+      <c r="F92" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="B93" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C93" s="10" t="s">
+      <c r="B93" s="9"/>
+      <c r="C93" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="E93" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="E93" s="9">
+      <c r="F93" s="9">
         <v>170606</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C94" s="10" t="s">
+      <c r="B94" s="9"/>
+      <c r="C94" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D94" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="E94" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="E94" s="9">
+      <c r="F94" s="9">
         <v>170120</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="B95" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C95" s="10" t="s">
+      <c r="B95" s="9"/>
+      <c r="C95" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D95" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="E95" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="E95" s="9">
+      <c r="F95" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B96" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C96" s="10" t="s">
+      <c r="B96" s="9"/>
+      <c r="C96" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D96" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="E96" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="E96" s="9">
+      <c r="F96" s="9">
         <v>170804</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="B97" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C97" s="10" t="s">
+      <c r="B97" s="9"/>
+      <c r="C97" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="E97" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="E97" s="9">
+      <c r="F97" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="9"/>
+      <c r="C98" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="D98" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="E98" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="E98" s="9">
+      <c r="F98" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="B99" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C99" s="10" t="s">
+      <c r="B99" s="9"/>
+      <c r="C99" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="E99" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="E99" s="9">
+      <c r="F99" s="9">
         <v>170156</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="9"/>
+      <c r="C100" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="D100" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="E100" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="E100" s="9">
+      <c r="F100" s="9">
         <v>170146</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B101" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C101" s="10" t="s">
+      <c r="B101" s="9"/>
+      <c r="C101" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D101" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="E101" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="E101" s="9">
+      <c r="F101" s="9">
         <v>170530</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="B102" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C102" s="10" t="s">
+      <c r="B102" s="9"/>
+      <c r="C102" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D102" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="E102" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="E102" s="9">
+      <c r="F102" s="9">
         <v>170517</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B103" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C103" s="10" t="s">
+      <c r="B103" s="9"/>
+      <c r="C103" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="E103" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="E103" s="9">
+      <c r="F103" s="9">
         <v>170170</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="9"/>
+      <c r="C104" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="D104" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="E104" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="E104" s="9">
+      <c r="F104" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="B105" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C105" s="10" t="s">
+      <c r="B105" s="9"/>
+      <c r="C105" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="E105" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="E105" s="9">
+      <c r="F105" s="9">
         <v>170503</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="B106" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C106" s="10" t="s">
+      <c r="B106" s="9"/>
+      <c r="C106" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D106" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="E106" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="E106" s="9">
+      <c r="F106" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="9"/>
+      <c r="C107" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="D107" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="E107" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="E107" s="9">
+      <c r="F107" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="9"/>
+      <c r="C108" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="D108" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="E108" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="E108" s="9">
+      <c r="F108" s="9">
         <v>170903</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="9"/>
+      <c r="C109" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="D109" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="E109" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="E109" s="9">
+      <c r="F109" s="9">
         <v>170134</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="9"/>
+      <c r="C110" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="D110" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="E110" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="E110" s="9">
+      <c r="F110" s="9">
         <v>170104</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" s="9"/>
+      <c r="C111" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="D111" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="E111" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="E111" s="9">
+      <c r="F111" s="9">
         <v>170134</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="B112" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C112" s="10" t="s">
+      <c r="B112" s="9"/>
+      <c r="C112" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D112" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="E112" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="E112" s="9">
+      <c r="F112" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="B113" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C113" s="10" t="s">
+      <c r="B113" s="9"/>
+      <c r="C113" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D113" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="E113" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="E113" s="9">
+      <c r="F113" s="9">
         <v>170904</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="9"/>
+      <c r="C114" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="D114" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="E114" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="E114" s="9">
+      <c r="F114" s="9">
         <v>170146</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B115" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C115" s="10" t="s">
+      <c r="B115" s="9"/>
+      <c r="C115" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D115" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="E115" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="E115" s="9">
+      <c r="F115" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B116" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C116" s="10" t="s">
+      <c r="B116" s="9"/>
+      <c r="C116" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D116" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="E116" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="E116" s="9">
+      <c r="F116" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="9"/>
+      <c r="C117" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="D117" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="E117" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="E117" s="9">
+      <c r="F117" s="9">
         <v>170135</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="B118" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C118" s="10" t="s">
+      <c r="B118" s="9"/>
+      <c r="C118" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D118" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="E118" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="E118" s="9">
+      <c r="F118" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="B119" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C119" s="10" t="s">
+      <c r="B119" s="9"/>
+      <c r="C119" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D119" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="E119" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="E119" s="9">
+      <c r="F119" s="9">
         <v>170521</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="9"/>
+      <c r="C120" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="D120" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="E120" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="E120" s="9">
+      <c r="F120" s="9">
         <v>170302</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="9"/>
+      <c r="C121" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="D121" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="D121" s="10" t="s">
+      <c r="E121" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="E121" s="9">
+      <c r="F121" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="B122" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C122" s="10" t="s">
+      <c r="B122" s="9"/>
+      <c r="C122" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D122" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="E122" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="E122" s="9">
+      <c r="F122" s="9">
         <v>170303</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="B123" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C123" s="10" t="s">
+      <c r="B123" s="9"/>
+      <c r="C123" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D123" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="E123" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="E123" s="9">
+      <c r="F123" s="9">
         <v>170136</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="B124" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C124" s="10" t="s">
+      <c r="B124" s="9"/>
+      <c r="C124" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D124" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="E124" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="E124" s="9">
+      <c r="F124" s="9">
         <v>170148</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="B125" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C125" s="10" t="s">
+      <c r="B125" s="9"/>
+      <c r="C125" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D125" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="E125" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="E125" s="9">
+      <c r="F125" s="9">
         <v>170155</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="9"/>
+      <c r="C126" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="D126" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="E126" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="E126" s="9">
+      <c r="F126" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="B127" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C127" s="10" t="s">
+      <c r="B127" s="9"/>
+      <c r="C127" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D127" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="E127" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="E127" s="9">
+      <c r="F127" s="9">
         <v>170135</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="B128" s="9" t="s">
+      <c r="B128" s="9"/>
+      <c r="C128" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="D128" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="E128" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="E128" s="9">
+      <c r="F128" s="9">
         <v>170528</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="B129" s="9" t="s">
+      <c r="B129" s="9"/>
+      <c r="C129" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="D129" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="E129" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="E129" s="9">
+      <c r="F129" s="9">
         <v>170130</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="B130" s="9" t="s">
+      <c r="B130" s="9"/>
+      <c r="C130" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="D130" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="E130" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="E130" s="9">
+      <c r="F130" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="B131" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C131" s="10" t="s">
+      <c r="B131" s="9"/>
+      <c r="C131" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D131" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="E131" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="E131" s="9">
+      <c r="F131" s="9">
         <v>170104</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="B132" s="9" t="s">
+      <c r="B132" s="9"/>
+      <c r="C132" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="D132" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="E132" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="E132" s="9">
+      <c r="F132" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B133" s="9" t="s">
+      <c r="B133" s="9"/>
+      <c r="C133" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="D133" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="E133" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="E133" s="9">
+      <c r="F133" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="B134" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C134" s="10" t="s">
+      <c r="B134" s="9"/>
+      <c r="C134" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D134" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="D134" s="10" t="s">
+      <c r="E134" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="E134" s="9">
+      <c r="F134" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" s="9"/>
+      <c r="C135" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C135" s="10" t="s">
+      <c r="D135" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="D135" s="10" t="s">
+      <c r="E135" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="E135" s="9">
+      <c r="F135" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="B136" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C136" s="10" t="s">
+      <c r="B136" s="9"/>
+      <c r="C136" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D136" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="E136" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="E136" s="9">
+      <c r="F136" s="9">
         <v>170805</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C137" s="10" t="s">
+      <c r="B137" s="9"/>
+      <c r="C137" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D137" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="D137" s="10" t="s">
+      <c r="E137" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="E137" s="9">
+      <c r="F137" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="B138" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C138" s="10" t="s">
+      <c r="B138" s="9"/>
+      <c r="C138" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D138" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="E138" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="E138" s="9">
+      <c r="F138" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B139" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C139" s="10" t="s">
+      <c r="B139" s="9"/>
+      <c r="C139" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="E139" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="E139" s="9">
+      <c r="F139" s="9">
         <v>170208</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="9"/>
+      <c r="C140" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="D140" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="D140" s="10" t="s">
+      <c r="E140" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="E140" s="9">
+      <c r="F140" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="B141" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C141" s="10" t="s">
+      <c r="B141" s="9"/>
+      <c r="C141" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D141" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="D141" s="10" t="s">
+      <c r="E141" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="E141" s="9">
+      <c r="F141" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="9"/>
+      <c r="C142" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="D142" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="D142" s="10" t="s">
+      <c r="E142" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="E142" s="9">
+      <c r="F142" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="B143" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C143" s="10" t="s">
+      <c r="B143" s="9"/>
+      <c r="C143" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D143" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="E143" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="E143" s="9">
+      <c r="F143" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="B144" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C144" s="10" t="s">
+      <c r="B144" s="9"/>
+      <c r="C144" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D144" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="E144" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="E144" s="9">
+      <c r="F144" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="B145" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C145" s="10" t="s">
+      <c r="B145" s="9"/>
+      <c r="C145" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D145" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="D145" s="10" t="s">
+      <c r="E145" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="E145" s="9">
+      <c r="F145" s="9">
         <v>170812</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="B146" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C146" s="10" t="s">
+      <c r="B146" s="9"/>
+      <c r="C146" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D146" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="E146" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="E146" s="9">
+      <c r="F146" s="9">
         <v>170103</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="9"/>
+      <c r="C147" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="D147" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="E147" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="E147" s="9">
+      <c r="F147" s="9">
         <v>170120</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="B148" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C148" s="10" t="s">
+      <c r="B148" s="9"/>
+      <c r="C148" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D148" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="D148" s="10" t="s">
+      <c r="E148" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="E148" s="9">
+      <c r="F148" s="9">
         <v>170141</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="B149" s="9" t="s">
+      <c r="B149" s="9"/>
+      <c r="C149" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="D149" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="E149" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="E149" s="9">
+      <c r="F149" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="B150" s="9" t="s">
+      <c r="B150" s="9"/>
+      <c r="C150" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="D150" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="D150" s="10" t="s">
+      <c r="E150" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="E150" s="9">
+      <c r="F150" s="9">
         <v>170803</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="B151" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C151" s="10" t="s">
+      <c r="B151" s="9"/>
+      <c r="C151" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D151" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="E151" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="E151" s="9">
+      <c r="F151" s="9">
         <v>170129</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="B152" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C152" s="10" t="s">
+      <c r="B152" s="9"/>
+      <c r="C152" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D152" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="D152" s="10" t="s">
+      <c r="E152" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="E152" s="9">
+      <c r="F152" s="9">
         <v>170808</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B153" s="9" t="s">
+      <c r="B153" s="9"/>
+      <c r="C153" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="D153" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="D153" s="10" t="s">
+      <c r="E153" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="E153" s="9">
+      <c r="F153" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="B154" s="9"/>
+      <c r="C154" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="D154" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="D154" s="10" t="s">
+      <c r="E154" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="E154" s="9">
+      <c r="F154" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="B155" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C155" s="10" t="s">
+      <c r="B155" s="9"/>
+      <c r="C155" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D155" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="D155" s="10" t="s">
+      <c r="E155" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="E155" s="9">
+      <c r="F155" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="9"/>
+      <c r="C156" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="D156" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="E156" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="E156" s="9">
+      <c r="F156" s="9">
         <v>170805</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="B157" s="9" t="s">
+      <c r="B157" s="9"/>
+      <c r="C157" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="D157" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="D157" s="10" t="s">
+      <c r="E157" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="E157" s="9">
+      <c r="F157" s="9">
         <v>170139</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="B158" s="9" t="s">
+      <c r="B158" s="9"/>
+      <c r="C158" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="D158" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="D158" s="10" t="s">
+      <c r="E158" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="E158" s="9">
+      <c r="F158" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B159" s="9"/>
+      <c r="C159" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="D159" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="E159" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="E159" s="9">
+      <c r="F159" s="9">
         <v>170148</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B160" s="9"/>
+      <c r="C160" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="D160" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="D160" s="10" t="s">
+      <c r="E160" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="E160" s="9">
+      <c r="F160" s="9">
         <v>170132</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="B161" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C161" s="10" t="s">
+      <c r="B161" s="9"/>
+      <c r="C161" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D161" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="D161" s="10" t="s">
+      <c r="E161" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="E161" s="9">
+      <c r="F161" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="B162" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C162" s="10" t="s">
+      <c r="B162" s="9"/>
+      <c r="C162" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D162" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="D162" s="10" t="s">
+      <c r="E162" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="E162" s="9">
+      <c r="F162" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="B163" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C163" s="10" t="s">
+      <c r="B163" s="9"/>
+      <c r="C163" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D163" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="D163" s="10" t="s">
+      <c r="E163" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="E163" s="9">
+      <c r="F163" s="9">
         <v>170502</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="9"/>
+      <c r="C164" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="D164" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="D164" s="10" t="s">
+      <c r="E164" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="E164" s="9">
+      <c r="F164" s="9">
         <v>170111</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="B165" s="9"/>
+      <c r="C165" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="D165" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="D165" s="10" t="s">
+      <c r="E165" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="E165" s="9">
+      <c r="F165" s="9">
         <v>170135</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="B166" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C166" s="10" t="s">
+      <c r="B166" s="9"/>
+      <c r="C166" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D166" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="D166" s="10" t="s">
+      <c r="E166" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="E166" s="9">
+      <c r="F166" s="9">
         <v>170102</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="B167" s="9" t="s">
+      <c r="B167" s="9"/>
+      <c r="C167" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="D167" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="D167" s="10" t="s">
+      <c r="E167" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="E167" s="9">
+      <c r="F167" s="9">
         <v>170156</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="B168" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C168" s="10" t="s">
+      <c r="B168" s="9"/>
+      <c r="C168" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D168" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="D168" s="10" t="s">
+      <c r="E168" s="10" t="s">
         <v>583</v>
       </c>
-      <c r="E168" s="9">
+      <c r="F168" s="9">
         <v>170134</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="B169" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C169" s="10" t="s">
+      <c r="B169" s="9"/>
+      <c r="C169" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D169" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="D169" s="10" t="s">
+      <c r="E169" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="E169" s="9">
+      <c r="F169" s="9">
         <v>170301</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="B170" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C170" s="10" t="s">
+      <c r="B170" s="9"/>
+      <c r="C170" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D170" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="D170" s="10" t="s">
+      <c r="E170" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="E170" s="9">
+      <c r="F170" s="9">
         <v>170120</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="B171" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C171" s="10" t="s">
+      <c r="B171" s="9"/>
+      <c r="C171" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D171" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="D171" s="10" t="s">
+      <c r="E171" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="E171" s="9">
+      <c r="F171" s="9">
         <v>170203</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="B172" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C172" s="10" t="s">
+      <c r="B172" s="9"/>
+      <c r="C172" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D172" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="D172" s="10" t="s">
+      <c r="E172" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="E172" s="9">
+      <c r="F172" s="9">
         <v>170120</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="B173" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C173" s="10" t="s">
+      <c r="B173" s="9"/>
+      <c r="C173" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D173" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="D173" s="10" t="s">
+      <c r="E173" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="E173" s="9">
+      <c r="F173" s="9">
         <v>170148</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="B174" s="9" t="s">
+      <c r="B174" s="9"/>
+      <c r="C174" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C174" s="10" t="s">
+      <c r="D174" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="E174" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="E174" s="9">
+      <c r="F174" s="9">
         <v>170129</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="B175" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C175" s="10" t="s">
+      <c r="B175" s="9"/>
+      <c r="C175" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D175" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="E175" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="E175" s="9">
+      <c r="F175" s="9">
         <v>170132</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="B176" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C176" s="10" t="s">
+      <c r="B176" s="9"/>
+      <c r="C176" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D176" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="D176" s="10" t="s">
+      <c r="E176" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="E176" s="9">
+      <c r="F176" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="B177" s="9" t="s">
+      <c r="B177" s="9"/>
+      <c r="C177" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="D177" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="D177" s="10" t="s">
+      <c r="E177" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="E177" s="9">
+      <c r="F177" s="9">
         <v>170511</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="B178" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C178" s="10" t="s">
+      <c r="B178" s="9"/>
+      <c r="C178" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D178" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="E178" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="E178" s="9">
+      <c r="F178" s="9">
         <v>170186</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B179" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C179" s="10" t="s">
+      <c r="B179" s="9"/>
+      <c r="C179" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D179" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="D179" s="10" t="s">
+      <c r="E179" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="E179" s="9">
+      <c r="F179" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="B180" s="9" t="s">
+      <c r="B180" s="9"/>
+      <c r="C180" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="D180" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="D180" s="10" t="s">
+      <c r="E180" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="E180" s="9">
+      <c r="F180" s="9">
         <v>170513</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="B181" s="9" t="s">
+      <c r="B181" s="9"/>
+      <c r="C181" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="D181" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="D181" s="10" t="s">
+      <c r="E181" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="E181" s="9">
+      <c r="F181" s="9">
         <v>170513</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="B182" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C182" s="10" t="s">
+      <c r="B182" s="9"/>
+      <c r="C182" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D182" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="D182" s="10" t="s">
+      <c r="E182" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="E182" s="9">
+      <c r="F182" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C183" s="10" t="s">
+      <c r="B183" s="9"/>
+      <c r="C183" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D183" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="D183" s="10" t="s">
+      <c r="E183" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="E183" s="9">
+      <c r="F183" s="9">
         <v>170148</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="B184" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C184" s="10" t="s">
+      <c r="B184" s="9"/>
+      <c r="C184" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D184" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="D184" s="10" t="s">
+      <c r="E184" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="E184" s="9">
+      <c r="F184" s="9">
         <v>170179</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="B185" s="9" t="s">
+      <c r="B185" s="9"/>
+      <c r="C185" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="D185" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="D185" s="10" t="s">
+      <c r="E185" s="10" t="s">
         <v>634</v>
       </c>
-      <c r="E185" s="9">
+      <c r="F185" s="9">
         <v>170146</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="9"/>
+      <c r="C186" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="D186" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="D186" s="10" t="s">
+      <c r="E186" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="E186" s="9">
+      <c r="F186" s="9">
         <v>170201</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="B187" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C187" s="10" t="s">
+      <c r="B187" s="9"/>
+      <c r="C187" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D187" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="D187" s="10" t="s">
+      <c r="E187" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="E187" s="9">
+      <c r="F187" s="9">
         <v>170146</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="B188" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C188" s="10" t="s">
+      <c r="B188" s="9"/>
+      <c r="C188" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D188" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="D188" s="10" t="s">
+      <c r="E188" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="E188" s="9">
+      <c r="F188" s="9">
         <v>170708</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="B189" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C189" s="10" t="s">
+      <c r="B189" s="9"/>
+      <c r="C189" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D189" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="D189" s="10" t="s">
+      <c r="E189" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="E189" s="9">
+      <c r="F189" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="B190" s="9" t="s">
+      <c r="B190" s="9"/>
+      <c r="C190" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="D190" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="D190" s="10" t="s">
+      <c r="E190" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="E190" s="9">
+      <c r="F190" s="9">
         <v>170179</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="B191" s="9" t="s">
+      <c r="B191" s="9"/>
+      <c r="C191" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="D191" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="D191" s="10" t="s">
+      <c r="E191" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="E191" s="9">
+      <c r="F191" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="B192" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C192" s="10" t="s">
+      <c r="B192" s="9"/>
+      <c r="C192" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D192" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="D192" s="10" t="s">
+      <c r="E192" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="E192" s="9">
+      <c r="F192" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B193" s="9"/>
+      <c r="C193" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="D193" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="D193" s="10" t="s">
+      <c r="E193" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="E193" s="9">
+      <c r="F193" s="9">
         <v>170138</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="B194" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C194" s="10" t="s">
+      <c r="B194" s="9"/>
+      <c r="C194" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D194" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="D194" s="10" t="s">
+      <c r="E194" s="10" t="s">
         <v>661</v>
       </c>
-      <c r="E194" s="9">
+      <c r="F194" s="9">
         <v>170131</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="B195" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C195" s="10" t="s">
+      <c r="B195" s="9"/>
+      <c r="C195" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D195" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="D195" s="10" t="s">
+      <c r="E195" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="E195" s="9">
+      <c r="F195" s="9">
         <v>170403</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="B196" s="9" t="s">
+      <c r="B196" s="9"/>
+      <c r="C196" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="D196" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="D196" s="10" t="s">
+      <c r="E196" s="10" t="s">
         <v>667</v>
       </c>
-      <c r="E196" s="9">
+      <c r="F196" s="9">
         <v>170517</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="B197" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C197" s="10" t="s">
+      <c r="B197" s="9"/>
+      <c r="C197" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D197" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="D197" s="10" t="s">
+      <c r="E197" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="E197" s="9">
+      <c r="F197" s="9">
         <v>170311</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="B198" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C198" s="10" t="s">
+      <c r="B198" s="9"/>
+      <c r="C198" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D198" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="D198" s="10" t="s">
+      <c r="E198" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="E198" s="9">
+      <c r="F198" s="9">
         <v>170202</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="B199" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C199" s="10" t="s">
+      <c r="B199" s="9"/>
+      <c r="C199" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D199" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="D199" s="10" t="s">
+      <c r="E199" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="E199" s="9">
+      <c r="F199" s="9">
         <v>170124</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="B200" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C200" s="10" t="s">
+      <c r="B200" s="9"/>
+      <c r="C200" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D200" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="D200" s="10" t="s">
+      <c r="E200" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="E200" s="9">
+      <c r="F200" s="9">
         <v>170184</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="B201" s="9" t="s">
+      <c r="B201" s="9"/>
+      <c r="C201" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="D201" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="D201" s="10" t="s">
+      <c r="E201" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="E201" s="9">
+      <c r="F201" s="9">
         <v>170402</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C202" s="10" t="s">
+      <c r="B202" s="9"/>
+      <c r="C202" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D202" s="10" t="s">
         <v>684</v>
       </c>
-      <c r="D202" s="10" t="s">
+      <c r="E202" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="E202" s="9">
+      <c r="F202" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="B203" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C203" s="10" t="s">
+      <c r="B203" s="9"/>
+      <c r="C203" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D203" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="D203" s="10" t="s">
+      <c r="E203" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="E203" s="9">
+      <c r="F203" s="9">
         <v>170170</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="B204" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C204" s="10" t="s">
+      <c r="B204" s="9"/>
+      <c r="C204" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D204" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="E204" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="E204" s="9">
+      <c r="F204" s="9">
         <v>170157</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="B205" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C205" s="10" t="s">
+      <c r="B205" s="9"/>
+      <c r="C205" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D205" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="D205" s="10" t="s">
+      <c r="E205" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="E205" s="9">
+      <c r="F205" s="9">
         <v>170129</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="B206" s="9" t="s">
+      <c r="B206" s="9"/>
+      <c r="C206" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C206" s="10" t="s">
+      <c r="D206" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="D206" s="10" t="s">
+      <c r="E206" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="E206" s="9">
+      <c r="F206" s="9">
         <v>170134</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="B207" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C207" s="10" t="s">
+      <c r="B207" s="9"/>
+      <c r="C207" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D207" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="D207" s="10" t="s">
+      <c r="E207" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="E207" s="9">
+      <c r="F207" s="9">
         <v>170205</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="B208" s="9" t="s">
+      <c r="B208" s="9"/>
+      <c r="C208" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C208" s="10" t="s">
+      <c r="D208" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="E208" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="E208" s="9">
+      <c r="F208" s="9">
         <v>170207</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="B209" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C209" s="10" t="s">
+      <c r="B209" s="9"/>
+      <c r="C209" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D209" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="E209" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="E209" s="9">
+      <c r="F209" s="9">
         <v>170401</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="B210" s="9" t="s">
+      <c r="B210" s="9"/>
+      <c r="C210" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="D210" s="10" t="s">
         <v>708</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="E210" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="E210" s="9">
+      <c r="F210" s="9">
         <v>170206</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="B211" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C211" s="10" t="s">
+      <c r="B211" s="9"/>
+      <c r="C211" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D211" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="E211" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="E211" s="9">
+      <c r="F211" s="9">
         <v>170133</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="B212" s="9" t="s">
+      <c r="B212" s="9"/>
+      <c r="C212" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="D212" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="E212" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="E212" s="9">
+      <c r="F212" s="9">
         <v>170144</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="B213" s="9"/>
+      <c r="C213" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="D213" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="E213" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="E213" s="9">
+      <c r="F213" s="9">
         <v>170121</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="B214" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C214" s="10" t="s">
+      <c r="B214" s="9"/>
+      <c r="C214" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D214" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="D214" s="10" t="s">
+      <c r="E214" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="E214" s="9">
+      <c r="F214" s="9">
         <v>170209</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="B215" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C215" s="10" t="s">
+      <c r="B215" s="9"/>
+      <c r="C215" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D215" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="E215" s="10" t="s">
         <v>724</v>
       </c>
-      <c r="E215" s="9">
+      <c r="F215" s="9">
         <v>170141</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="B216" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C216" s="10" t="s">
+      <c r="B216" s="9"/>
+      <c r="C216" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D216" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="D216" s="10" t="s">
+      <c r="E216" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="E216" s="9">
+      <c r="F216" s="9">
         <v>170136</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="B217" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C217" s="10" t="s">
+      <c r="B217" s="9"/>
+      <c r="C217" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D217" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="D217" s="10" t="s">
+      <c r="E217" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="E217" s="9">
+      <c r="F217" s="9">
         <v>170208</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="B218" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C218" s="10" t="s">
+      <c r="B218" s="9"/>
+      <c r="C218" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D218" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="E218" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="E218" s="9">
+      <c r="F218" s="9">
         <v>170601</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="B219" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C219" s="10" t="s">
+      <c r="B219" s="9"/>
+      <c r="C219" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D219" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="E219" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="E219" s="9">
+      <c r="F219" s="9">
         <v>170126</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B220" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C220" s="15" t="s">
+      <c r="B220" s="12"/>
+      <c r="C220" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D220" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="D220" s="15" t="s">
+      <c r="E220" s="15" t="s">
         <v>738</v>
       </c>
-      <c r="E220" s="12">
+      <c r="F220" s="12">
         <v>170136</v>
       </c>
     </row>
